--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importContractInsure.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importContractInsure.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25757\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D856623-8AF2-4729-8E2B-AFC2A5A72271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E46F0B00-EE51-4142-8DDE-5C82D65B9EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2023-07-05" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -23,34 +23,22 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>保险名称</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>保险金额</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -61,6 +49,24 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -110,10 +116,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -134,7 +140,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -150,7 +156,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -162,7 +168,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -179,9 +185,9 @@
         <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -214,9 +220,9 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -392,25 +398,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16.6640625" customWidth="1"/>
+    <col min="1" max="2" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importContractInsure.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importContractInsure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E46F0B00-EE51-4142-8DDE-5C82D65B9EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC6D4FF-6AD3-4094-8D66-A3CC9CBFEC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -67,6 +67,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -112,7 +118,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -121,6 +127,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -400,23 +415,31 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16.625" customWidth="1"/>
+    <col min="1" max="1" width="16.625" customWidth="1"/>
+    <col min="2" max="2" width="16.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
+      <c r="B2" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B1048576" xr:uid="{76EF1EA5-E52A-403A-B42D-2F72D69EAF54}">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importContractInsure.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importContractInsure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC6D4FF-6AD3-4094-8D66-A3CC9CBFEC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E080A5FA-BD6A-4227-BFE6-C567B4DA6959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,13 +128,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -429,7 +429,9 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="4"/>
+      <c r="B2" s="4">
+        <v>1.01</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importContractInsure.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/importContractInsure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fushudong\workspace20230814\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E080A5FA-BD6A-4227-BFE6-C567B4DA6959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{135AEF00-0DEC-48F7-88C2-ABCE8CD291D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -429,9 +429,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
-      <c r="B2" s="4">
-        <v>1.01</v>
-      </c>
+      <c r="B2" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
